--- a/AAII_Financials/Quarterly/VOYA_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/VOYA_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="325" uniqueCount="92">
   <si>
     <t>VOYA</t>
   </si>
@@ -656,515 +656,527 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AP102"/>
+  <dimension ref="A5:AQ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="42" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="43" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="43" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="44" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:43" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44742</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44651</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44561</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44469</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44377</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44286</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44196</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44104</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>44012</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43921</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43830</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43738</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43646</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43555</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43465</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43373</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43190</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43100</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>43008</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42916</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42825</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AP7" s="2">
         <v>42735</v>
       </c>
-      <c r="AP7" s="2">
+      <c r="AQ7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1896000</v>
+      </c>
+      <c r="E8" s="3">
         <v>2031000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>2111000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>2128000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1981000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1969000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>2010000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1956000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>2033000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>2051000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1819000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1823000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1871000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>1835000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>1538000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>1345000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>1524000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>1506000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>1677000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>2009000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>2503000</v>
       </c>
-      <c r="X8" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Y8" s="3">
+      <c r="Y8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z8" s="3">
         <v>2231000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>5505000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>1719000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>1705000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>1844000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>1878000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>1972000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>1848000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>837000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>2259000</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>2114000</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>1981000</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>1281400</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>2185000</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>2192000</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>2059000</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AP8" s="3">
         <v>8822000</v>
       </c>
-      <c r="AP8" s="3">
+      <c r="AQ8" s="3">
         <v>2541200</v>
       </c>
     </row>
-    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>887000</v>
+      </c>
+      <c r="E9" s="3">
         <v>884000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>939000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>915000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>859000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>897000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>1043000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>993000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>899000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>907000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>861000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>856000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>739000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>810000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>83000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>60000</v>
-      </c>
-      <c r="S9" s="3">
-        <v>62000</v>
       </c>
       <c r="T9" s="3">
         <v>62000</v>
       </c>
       <c r="U9" s="3">
+        <v>62000</v>
+      </c>
+      <c r="V9" s="3">
         <v>40000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>190000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>26000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>539000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>16000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>336000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>19000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>76000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>46000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>36000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>43000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>57000</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>-27000</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>86000</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>74000</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>100000</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>-34400</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>209000</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3">
         <v>195000</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AO9" s="3">
         <v>64000</v>
       </c>
-      <c r="AO9" s="3">
+      <c r="AP9" s="3">
         <v>415000</v>
       </c>
-      <c r="AP9" s="3">
+      <c r="AQ9" s="3">
         <v>180700</v>
       </c>
     </row>
-    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>1009000</v>
+      </c>
+      <c r="E10" s="3">
         <v>1147000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>1172000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>1213000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>1122000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>1072000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>967000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>963000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>1134000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>1144000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>958000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>967000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>1132000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>1025000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>1455000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>1285000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>1462000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>1444000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>1637000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>1819000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>2477000</v>
       </c>
-      <c r="X10" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Y10" s="3">
+      <c r="Y10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z10" s="3">
         <v>2215000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>5169000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>1700000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>1629000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>1798000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>1842000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>1929000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>1791000</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>864000</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>2173000</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>2040000</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>1881000</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>1315800</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>1976000</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AN10" s="3">
         <v>1997000</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AO10" s="3">
         <v>1995000</v>
       </c>
-      <c r="AO10" s="3">
+      <c r="AP10" s="3">
         <v>8407000</v>
       </c>
-      <c r="AP10" s="3">
+      <c r="AQ10" s="3">
         <v>2360500</v>
       </c>
     </row>
-    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1207,8 +1219,9 @@
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
       <c r="AP11" s="3"/>
+      <c r="AQ11" s="3"/>
     </row>
-    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1329,8 +1342,11 @@
       <c r="AP12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AQ12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1451,8 +1467,11 @@
       <c r="AP13" s="3">
         <v>0</v>
       </c>
+      <c r="AQ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1483,83 +1502,83 @@
       <c r="L14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M14" s="3">
+      <c r="M14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N14" s="3">
         <v>70000</v>
       </c>
-      <c r="N14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="O14" s="3">
+      <c r="O14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P14" s="3">
         <v>12000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>2000</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>80000</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>15000</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>2000</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>10000</v>
-      </c>
-      <c r="U14" s="3">
-        <v>3000</v>
       </c>
       <c r="V14" s="3">
         <v>3000</v>
       </c>
       <c r="W14" s="3">
+        <v>3000</v>
+      </c>
+      <c r="X14" s="3">
         <v>13000</v>
       </c>
-      <c r="X14" s="3">
-        <v>0</v>
-      </c>
       <c r="Y14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z14" s="3">
         <v>1000</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>80000</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>50000</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>20000</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>31000</v>
-      </c>
-      <c r="AD14" s="3">
-        <v>3000</v>
       </c>
       <c r="AE14" s="3">
         <v>3000</v>
       </c>
       <c r="AF14" s="3">
+        <v>3000</v>
+      </c>
+      <c r="AG14" s="3">
         <v>26000</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>6000</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>7000</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AJ14" s="3">
         <v>1000</v>
       </c>
-      <c r="AJ14" s="3">
+      <c r="AK14" s="3">
         <v>14000</v>
       </c>
-      <c r="AK14" s="3">
+      <c r="AL14" s="3">
         <v>15800</v>
-      </c>
-      <c r="AL14" s="3">
-        <v>1000</v>
       </c>
       <c r="AM14" s="3">
         <v>1000</v>
@@ -1568,13 +1587,16 @@
         <v>1000</v>
       </c>
       <c r="AO14" s="3">
+        <v>1000</v>
+      </c>
+      <c r="AP14" s="3">
         <v>34000</v>
       </c>
-      <c r="AP14" s="3">
+      <c r="AQ14" s="3">
         <v>12700</v>
       </c>
     </row>
-    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1582,44 +1604,44 @@
         <v>29000</v>
       </c>
       <c r="E15" s="3">
+        <v>29000</v>
+      </c>
+      <c r="F15" s="3">
         <v>27000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>26000</v>
-      </c>
-      <c r="G15" s="3">
-        <v>25000</v>
       </c>
       <c r="H15" s="3">
         <v>25000</v>
       </c>
       <c r="I15" s="3">
+        <v>25000</v>
+      </c>
+      <c r="J15" s="3">
         <v>26000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>24000</v>
-      </c>
-      <c r="K15" s="3">
-        <v>23000</v>
       </c>
       <c r="L15" s="3">
         <v>23000</v>
       </c>
       <c r="M15" s="3">
+        <v>23000</v>
+      </c>
+      <c r="N15" s="3">
         <v>22000</v>
-      </c>
-      <c r="N15" s="3">
-        <v>21000</v>
       </c>
       <c r="O15" s="3">
         <v>21000</v>
       </c>
       <c r="P15" s="3">
+        <v>21000</v>
+      </c>
+      <c r="Q15" s="3">
         <v>9000</v>
       </c>
-      <c r="Q15" s="3">
-        <v>0</v>
-      </c>
       <c r="R15" s="3">
         <v>0</v>
       </c>
@@ -1695,8 +1717,11 @@
       <c r="AP15" s="3">
         <v>0</v>
       </c>
+      <c r="AQ15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:43" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1736,252 +1761,259 @@
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
       <c r="AP16" s="3"/>
+      <c r="AQ16" s="3"/>
     </row>
-    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1794000</v>
+      </c>
+      <c r="E17" s="3">
         <v>1740000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1885000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1761000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1730000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>1729000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1815000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1771000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1659000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1707000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1567000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1575000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1502000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1644000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>1407000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>1231000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>1326000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>1338000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>1308000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>1548000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>1424000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>-3049000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>1682000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>5510000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>1711000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>1618000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>1716000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>1670000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>1671000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>1699000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>667000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>2018000</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>1811000</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>1905000</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>1000900</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>2078000</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>1965000</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>1883000</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AP17" s="3">
         <v>8422000</v>
       </c>
-      <c r="AP17" s="3">
+      <c r="AQ17" s="3">
         <v>2825000</v>
       </c>
     </row>
-    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>102000</v>
+      </c>
+      <c r="E18" s="3">
         <v>291000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>226000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>367000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>251000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>240000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>195000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>185000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>374000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>344000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>252000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>248000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>369000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>191000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>131000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>114000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>198000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>168000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>369000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>461000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>1079000</v>
       </c>
-      <c r="X18" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Y18" s="3">
+      <c r="Y18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z18" s="3">
         <v>549000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-5000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>8000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>87000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>128000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>208000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>301000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>149000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>170000</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>241000</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>303000</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>76000</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>280500</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>107000</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>227000</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>176000</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AP18" s="3">
         <v>400000</v>
       </c>
-      <c r="AP18" s="3">
+      <c r="AQ18" s="3">
         <v>-283800</v>
       </c>
     </row>
-    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -2024,8 +2056,9 @@
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
       <c r="AP19" s="3"/>
+      <c r="AQ19" s="3"/>
     </row>
-    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -2068,8 +2101,8 @@
       <c r="P20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q20" s="3">
-        <v>0</v>
+      <c r="Q20" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R20" s="3">
         <v>0</v>
@@ -2089,11 +2122,11 @@
       <c r="W20" s="3">
         <v>0</v>
       </c>
-      <c r="X20" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Y20" s="3">
-        <v>0</v>
+      <c r="X20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y20" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Z20" s="3">
         <v>0</v>
@@ -2146,65 +2179,68 @@
       <c r="AP20" s="3">
         <v>0</v>
       </c>
+      <c r="AQ20" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>131000</v>
+      </c>
+      <c r="E21" s="3">
         <v>320000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>253000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>393000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>276000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>265000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>221000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>209000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>397000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>367000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>274000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>269000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>390000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>200000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>130000</v>
       </c>
-      <c r="R21" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="S21" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="T21" s="3">
+      <c r="T21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="U21" s="3">
         <v>179000</v>
       </c>
-      <c r="U21" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="V21" s="3" t="s">
         <v>8</v>
       </c>
@@ -2214,15 +2250,15 @@
       <c r="X21" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Y21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z21" s="3">
         <v>549000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>-5000</v>
       </c>
-      <c r="AA21" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AB21" s="3" t="s">
         <v>8</v>
       </c>
@@ -2268,374 +2304,386 @@
       <c r="AP21" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AQ21" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>68000</v>
+      </c>
+      <c r="E22" s="3">
         <v>61000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>57000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>60000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>63000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>67000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>75000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>69000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>98000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>57000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>80000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>76000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>94000</v>
-      </c>
-      <c r="P22" s="3">
-        <v>48000</v>
       </c>
       <c r="Q22" s="3">
         <v>48000</v>
       </c>
       <c r="R22" s="3">
+        <v>48000</v>
+      </c>
+      <c r="S22" s="3">
         <v>43000</v>
-      </c>
-      <c r="S22" s="3">
-        <v>46000</v>
       </c>
       <c r="T22" s="3">
         <v>46000</v>
       </c>
       <c r="U22" s="3">
+        <v>46000</v>
+      </c>
+      <c r="V22" s="3">
         <v>69000</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>50000</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>51000</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>54000</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>48000</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>138000</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>50000</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>43000</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>48000</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>59000</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>58000</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>47000</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>90000</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>55000</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>62000</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>55000</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AL22" s="3">
         <v>62300</v>
       </c>
-      <c r="AL22" s="3">
+      <c r="AM22" s="3">
         <v>67000</v>
       </c>
-      <c r="AM22" s="3">
+      <c r="AN22" s="3">
         <v>72000</v>
       </c>
-      <c r="AN22" s="3">
+      <c r="AO22" s="3">
         <v>63000</v>
       </c>
-      <c r="AO22" s="3">
+      <c r="AP22" s="3">
         <v>390000</v>
       </c>
-      <c r="AP22" s="3">
+      <c r="AQ22" s="3">
         <v>72100</v>
       </c>
     </row>
-    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>34000</v>
+      </c>
+      <c r="E23" s="3">
         <v>230000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>169000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>307000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>188000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>173000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>120000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>116000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>276000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>287000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>102000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>172000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>263000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>141000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>83000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>71000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>152000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>122000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>300000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>411000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>1028000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>1038000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>501000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-143000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-42000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>44000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>80000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>149000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>243000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>102000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>80000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>186000</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>241000</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>21000</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>218200</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>40000</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>155000</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>113000</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AP23" s="3">
         <v>10000</v>
       </c>
-      <c r="AP23" s="3">
+      <c r="AQ23" s="3">
         <v>-355900</v>
       </c>
     </row>
-    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>16000</v>
+      </c>
+      <c r="E24" s="3">
         <v>35000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>20000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>35000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>27000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>22000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-1000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>18000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>41000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-1000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-17000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-74000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>28000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>12000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-54000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>29000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>9000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>11000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-202000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>40000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>112000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>-48000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>55000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>-72000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>6000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>-6000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>-264000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>5000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>33000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>9000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>-41000</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>21000</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>45000</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>4000</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>42000</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>-40000</v>
       </c>
-      <c r="AM24" s="3">
-        <v>0</v>
-      </c>
       <c r="AN24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO24" s="3">
         <v>93000</v>
       </c>
-      <c r="AO24" s="3">
+      <c r="AP24" s="3">
         <v>-29000</v>
       </c>
-      <c r="AP24" s="3">
+      <c r="AQ24" s="3">
         <v>-119400</v>
       </c>
     </row>
-    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2756,252 +2804,261 @@
       <c r="AP25" s="3">
         <v>0</v>
       </c>
+      <c r="AQ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>18000</v>
+      </c>
+      <c r="E26" s="3">
         <v>195000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>149000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>272000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>161000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>151000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>121000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>98000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>235000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>288000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>119000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>246000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>235000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>129000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>137000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>42000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>143000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>111000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>502000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>371000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>916000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>1086000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>446000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-71000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-48000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>50000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>344000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>144000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>210000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>93000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>121000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>165000</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>196000</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>17000</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>176200</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>80000</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>155000</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>20000</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AP26" s="3">
         <v>39000</v>
       </c>
-      <c r="AP26" s="3">
+      <c r="AQ26" s="3">
         <v>-236500</v>
       </c>
     </row>
-    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>90000</v>
+      </c>
+      <c r="E27" s="3">
         <v>165000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>136000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>176000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>162000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>139000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>93000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>98000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>201000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>234000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>118000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>248000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>154000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>69000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>190000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>166000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>64000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>54000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>398000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>143000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>465000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>1072000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>318000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-136000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>27000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>30000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>334000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>111000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>184000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>84000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>57000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>142000</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>138000</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>17000</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>94700</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>15000</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>103000</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>19000</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AP27" s="3">
         <v>10000</v>
       </c>
-      <c r="AP27" s="3">
+      <c r="AQ27" s="3">
         <v>-248100</v>
       </c>
     </row>
-    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3122,8 +3179,11 @@
       <c r="AP28" s="3">
         <v>0</v>
       </c>
+      <c r="AQ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3179,73 +3239,76 @@
         <v>0</v>
       </c>
       <c r="U29" s="3">
+        <v>0</v>
+      </c>
+      <c r="V29" s="3">
         <v>5000</v>
       </c>
-      <c r="V29" s="3">
+      <c r="W29" s="3">
         <v>-1000</v>
       </c>
-      <c r="W29" s="3">
+      <c r="X29" s="3">
         <v>-6000</v>
       </c>
-      <c r="X29" s="3">
+      <c r="Y29" s="3">
         <v>14000</v>
       </c>
-      <c r="Y29" s="3">
+      <c r="Z29" s="3">
         <v>-58000</v>
       </c>
-      <c r="Z29" s="3">
+      <c r="AA29" s="3">
         <v>-363000</v>
       </c>
-      <c r="AA29" s="3">
+      <c r="AB29" s="3">
         <v>-93000</v>
       </c>
-      <c r="AB29" s="3">
+      <c r="AC29" s="3">
         <v>-128000</v>
       </c>
-      <c r="AC29" s="3">
+      <c r="AD29" s="3">
         <v>-1119000</v>
       </c>
-      <c r="AD29" s="3">
+      <c r="AE29" s="3">
         <v>-4000</v>
       </c>
-      <c r="AE29" s="3">
+      <c r="AF29" s="3">
         <v>42000</v>
       </c>
-      <c r="AF29" s="3">
+      <c r="AG29" s="3">
         <v>-20000</v>
       </c>
-      <c r="AG29" s="3">
+      <c r="AH29" s="3">
         <v>64000</v>
       </c>
-      <c r="AH29" s="3">
-        <v>0</v>
-      </c>
       <c r="AI29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ29" s="3">
         <v>28000</v>
       </c>
-      <c r="AJ29" s="3">
+      <c r="AK29" s="3">
         <v>429000</v>
       </c>
-      <c r="AK29" s="3">
+      <c r="AL29" s="3">
         <v>-3259000</v>
       </c>
-      <c r="AL29" s="3">
+      <c r="AM29" s="3">
         <v>134000</v>
       </c>
-      <c r="AM29" s="3">
+      <c r="AN29" s="3">
         <v>64000</v>
       </c>
-      <c r="AN29" s="3">
+      <c r="AO29" s="3">
         <v>-162000</v>
       </c>
-      <c r="AO29" s="3">
+      <c r="AP29" s="3">
         <v>-337000</v>
       </c>
-      <c r="AP29" s="3" t="s">
+      <c r="AQ29" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3366,8 +3429,11 @@
       <c r="AP30" s="3">
         <v>0</v>
       </c>
+      <c r="AQ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3488,8 +3554,11 @@
       <c r="AP31" s="3">
         <v>0</v>
       </c>
+      <c r="AQ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3532,8 +3601,8 @@
       <c r="P32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q32" s="3">
-        <v>0</v>
+      <c r="Q32" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R32" s="3">
         <v>0</v>
@@ -3553,11 +3622,11 @@
       <c r="W32" s="3">
         <v>0</v>
       </c>
-      <c r="X32" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Y32" s="3">
-        <v>0</v>
+      <c r="X32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y32" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Z32" s="3">
         <v>0</v>
@@ -3610,130 +3679,136 @@
       <c r="AP32" s="3">
         <v>0</v>
       </c>
+      <c r="AQ32" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>94000</v>
+      </c>
+      <c r="E33" s="3">
         <v>182000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>140000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>192000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>166000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>156000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>97000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>114000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>205000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>251000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>122000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>262000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>158000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>83000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>190000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>166000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>64000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>54000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>403000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>142000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>459000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>1086000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>260000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-499000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-66000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-98000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-785000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>107000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>226000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>64000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>121000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>142000</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>166000</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>446000</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>-3164300</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>149000</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>167000</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>-143000</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AP33" s="3">
         <v>-327000</v>
       </c>
-      <c r="AP33" s="3">
+      <c r="AQ33" s="3">
         <v>-248100</v>
       </c>
     </row>
-    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3854,257 +3929,266 @@
       <c r="AP34" s="3">
         <v>0</v>
       </c>
+      <c r="AQ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>94000</v>
+      </c>
+      <c r="E35" s="3">
         <v>182000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>140000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>192000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>166000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>156000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>97000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>114000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>205000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>251000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>122000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>262000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>158000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>83000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>190000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>166000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>64000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>54000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>403000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>142000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>459000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>1086000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>260000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-499000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-66000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-98000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-785000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>107000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>226000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>64000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>121000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>142000</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>166000</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>446000</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>-3164300</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>149000</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>167000</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>-143000</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AP35" s="3">
         <v>-327000</v>
       </c>
-      <c r="AP35" s="3">
+      <c r="AQ35" s="3">
         <v>-248100</v>
       </c>
     </row>
-    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44742</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44651</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44561</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44469</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44377</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44286</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44196</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44104</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>44012</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43921</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43830</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43738</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43646</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43555</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43465</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43373</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43190</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43100</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>43008</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42916</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42825</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AP38" s="2">
         <v>42735</v>
       </c>
-      <c r="AP38" s="2">
+      <c r="AQ38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4147,8 +4231,9 @@
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
       <c r="AP39" s="3"/>
+      <c r="AQ39" s="3"/>
     </row>
-    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4191,175 +4276,179 @@
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
       <c r="AP40" s="3"/>
+      <c r="AQ40" s="3"/>
     </row>
-    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1008000</v>
+      </c>
+      <c r="E41" s="3">
         <v>969000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1228000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1157000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>1179000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>868000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1399000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1457000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1066000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>995000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>937000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>829000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1195000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>724000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>1007000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>935000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>1039000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>1125000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>1573000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>1818000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>1850000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>1316000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>1723000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>1136000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>1149000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>1085000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>1249000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>1450000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>1541000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>1340000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>1568000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>1885000</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>1620000</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>1597000</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>1435000</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>2072900</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>2713300</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>2531300</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AP41" s="3">
         <v>2229000</v>
       </c>
-      <c r="AP41" s="3">
+      <c r="AQ41" s="3">
         <v>2951600</v>
       </c>
     </row>
-    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>359000</v>
+      </c>
+      <c r="E42" s="3">
         <v>403000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>329000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>345000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>366000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>357000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>340000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>298000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>367000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>506000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>483000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>704000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>423000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>309000</v>
       </c>
-      <c r="Q42" s="3">
-        <v>0</v>
-      </c>
       <c r="R42" s="3">
         <v>0</v>
       </c>
@@ -4435,71 +4524,74 @@
       <c r="AP42" s="3">
         <v>0</v>
       </c>
+      <c r="AQ42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>310000</v>
+      </c>
+      <c r="E43" s="3">
         <v>305000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>346000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>331000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>314000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>334000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>350000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>323000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>300000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>335000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>322000</v>
       </c>
-      <c r="N43" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="O43" s="3" t="s">
         <v>8</v>
       </c>
       <c r="P43" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="Q43" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R43" s="3">
         <v>12426000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>13561000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>13079000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>13261000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>13635000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>13580000</v>
       </c>
-      <c r="W43" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="X43" s="3" t="s">
         <v>8</v>
       </c>
@@ -4512,8 +4604,8 @@
       <c r="AA43" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AB43" s="3">
-        <v>0</v>
+      <c r="AB43" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AC43" s="3">
         <v>0</v>
@@ -4557,8 +4649,11 @@
       <c r="AP43" s="3">
         <v>0</v>
       </c>
+      <c r="AQ43" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -4601,8 +4696,8 @@
       <c r="P44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q44" s="3">
-        <v>0</v>
+      <c r="Q44" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R44" s="3">
         <v>0</v>
@@ -4679,53 +4774,56 @@
       <c r="AP44" s="3">
         <v>0</v>
       </c>
+      <c r="AQ44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>11929000</v>
+      </c>
+      <c r="E45" s="3">
         <v>12217000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>12284000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>12417000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>12556000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>12809000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>12917000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>13298000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>13160000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>13476000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>13647000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>13296000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>13899000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>14330000</v>
       </c>
-      <c r="Q45" s="3">
-        <v>0</v>
-      </c>
       <c r="R45" s="3">
         <v>0</v>
       </c>
@@ -4801,53 +4899,56 @@
       <c r="AP45" s="3">
         <v>0</v>
       </c>
+      <c r="AQ45" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>13606000</v>
+      </c>
+      <c r="E46" s="3">
         <v>13894000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>14351000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>14250000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>14415000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>14368000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>15198000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>15376000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>14893000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>15312000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>15389000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>14810000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>15479000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>15328000</v>
       </c>
-      <c r="Q46" s="3">
-        <v>0</v>
-      </c>
       <c r="R46" s="3">
         <v>0</v>
       </c>
@@ -4923,130 +5024,136 @@
       <c r="AP46" s="3">
         <v>0</v>
       </c>
+      <c r="AQ46" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>27559000</v>
+      </c>
+      <c r="E47" s="3">
         <v>27981000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>28518000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>28398000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>27906000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>27883000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>26015000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>26895000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>26353000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>26599000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>27352000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>27003000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>28304000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>29534000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>38086000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>38408000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>39911000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>41978000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>44387000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>47491000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>45341000</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>44660000</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>54841000</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>54357000</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>54264000</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>51772000</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>52700000</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>67153000</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>65417000</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>64204000</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>49918000</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>62277000</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>62241000</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>63014000</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>64644000</v>
       </c>
-      <c r="AL47" s="3">
+      <c r="AM47" s="3">
         <v>93681000</v>
       </c>
-      <c r="AM47" s="3">
+      <c r="AN47" s="3">
         <v>90575600</v>
       </c>
-      <c r="AN47" s="3">
+      <c r="AO47" s="3">
         <v>89116700</v>
       </c>
-      <c r="AO47" s="3">
+      <c r="AP47" s="3">
         <v>61153000</v>
       </c>
-      <c r="AP47" s="3">
+      <c r="AQ47" s="3">
         <v>93051100</v>
       </c>
     </row>
-    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -5089,8 +5196,8 @@
       <c r="P48" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q48" s="3">
-        <v>0</v>
+      <c r="Q48" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R48" s="3">
         <v>0</v>
@@ -5143,83 +5250,86 @@
       <c r="AH48" s="3">
         <v>0</v>
       </c>
-      <c r="AI48" s="3" t="s">
-        <v>8</v>
+      <c r="AI48" s="3">
+        <v>0</v>
       </c>
       <c r="AJ48" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AK48" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AL48" s="3">
         <v>107000</v>
       </c>
-      <c r="AL48" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AM48" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AN48" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AO48" s="3">
+      <c r="AO48" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AP48" s="3">
         <v>112300</v>
       </c>
-      <c r="AP48" s="3" t="s">
+      <c r="AQ48" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>3986000</v>
+      </c>
+      <c r="E49" s="3">
         <v>4032000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>4079000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>4076000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>4115000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>4163000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>3728000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>3783000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>3800000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>3831000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>3855000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>3926000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>3858000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>3884000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>958000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>824000</v>
       </c>
-      <c r="S49" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="T49" s="3" t="s">
         <v>8</v>
       </c>
@@ -5235,8 +5345,8 @@
       <c r="X49" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y49" s="3">
-        <v>0</v>
+      <c r="Y49" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Z49" s="3">
         <v>0</v>
@@ -5265,32 +5375,35 @@
       <c r="AH49" s="3">
         <v>0</v>
       </c>
-      <c r="AI49" s="3" t="s">
-        <v>8</v>
+      <c r="AI49" s="3">
+        <v>0</v>
       </c>
       <c r="AJ49" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AK49" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AL49" s="3">
         <v>186000</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>196000</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AN49" s="3">
         <v>197800</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AO49" s="3">
         <v>208000</v>
       </c>
-      <c r="AO49" s="3">
+      <c r="AP49" s="3">
         <v>219500</v>
       </c>
-      <c r="AP49" s="3">
+      <c r="AQ49" s="3">
         <v>227300</v>
       </c>
     </row>
-    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5411,8 +5524,11 @@
       <c r="AP50" s="3">
         <v>0</v>
       </c>
+      <c r="AQ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5533,130 +5649,136 @@
       <c r="AP51" s="3">
         <v>0</v>
       </c>
+      <c r="AQ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>130152000</v>
+      </c>
+      <c r="E52" s="3">
         <v>119665000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>124031000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>123132000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>118178000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>109583000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>111692000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>113757000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>108741000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>108270000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>102687000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>95386000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>99117000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>94652000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>2223000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>1931000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>1795000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>1405000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>986000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>691000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>690000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>935000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>21889000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>21494000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>21249000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>20902000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>22953000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>401000</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>576000</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>864000</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>21655000</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>1122000</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>1266000</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>58102000</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>59833000</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>1663700</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AN52" s="3">
         <v>1756900</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AO52" s="3">
         <v>2055700</v>
       </c>
-      <c r="AO52" s="3">
+      <c r="AP52" s="3">
         <v>66368800</v>
       </c>
-      <c r="AP52" s="3">
+      <c r="AQ52" s="3">
         <v>1128100</v>
       </c>
     </row>
-    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5777,130 +5899,136 @@
       <c r="AP53" s="3">
         <v>0</v>
       </c>
+      <c r="AQ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>182946000</v>
+      </c>
+      <c r="E54" s="3">
         <v>173433000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>178859000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>177448000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>172436000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>163950000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>163889000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>166933000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>161280000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>161631000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>157085000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>149265000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>154616000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>151208000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>146606000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>144048000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>147520000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>161806000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>171262000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>168417000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>168194000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>162861000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>180518000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>171466000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>166934000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>155732000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>168990000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>166850000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>165162000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>161985000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>155430000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>165036000</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>162740000</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>219824000</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>222532000</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>226643900</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>219838800</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>217025500</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AP54" s="3">
         <v>214585000</v>
       </c>
-      <c r="AP54" s="3">
+      <c r="AQ54" s="3">
         <v>218622200</v>
       </c>
     </row>
-    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5943,8 +6071,9 @@
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
       <c r="AP55" s="3"/>
+      <c r="AQ55" s="3"/>
     </row>
-    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5987,8 +6116,9 @@
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
       <c r="AP56" s="3"/>
+      <c r="AQ56" s="3"/>
     </row>
-    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -6031,8 +6161,8 @@
       <c r="P57" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q57" s="3">
-        <v>0</v>
+      <c r="Q57" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R57" s="3">
         <v>0</v>
@@ -6109,58 +6239,61 @@
       <c r="AP57" s="3">
         <v>0</v>
       </c>
+      <c r="AQ57" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>2400000</v>
+      </c>
+      <c r="E58" s="3">
         <v>2768000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>2923000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>2979000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>2908000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>2551000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>2861000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>1765000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>1610000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>1613000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>1122000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>1192000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>1444000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>1471000</v>
-      </c>
-      <c r="Q58" s="3">
-        <v>141000</v>
       </c>
       <c r="R58" s="3">
         <v>141000</v>
       </c>
       <c r="S58" s="3">
-        <v>1000</v>
+        <v>141000</v>
       </c>
       <c r="T58" s="3">
         <v>1000</v>
@@ -6196,10 +6329,10 @@
         <v>1000</v>
       </c>
       <c r="AE58" s="3">
+        <v>1000</v>
+      </c>
+      <c r="AF58" s="3">
         <v>97000</v>
-      </c>
-      <c r="AF58" s="3">
-        <v>1000</v>
       </c>
       <c r="AG58" s="3">
         <v>1000</v>
@@ -6211,28 +6344,31 @@
         <v>1000</v>
       </c>
       <c r="AJ58" s="3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL58" s="3">
         <v>337000</v>
       </c>
-      <c r="AL58" s="3">
+      <c r="AM58" s="3">
         <v>336600</v>
       </c>
-      <c r="AM58" s="3">
+      <c r="AN58" s="3">
         <v>735900</v>
       </c>
-      <c r="AN58" s="3">
+      <c r="AO58" s="3">
         <v>735500</v>
       </c>
-      <c r="AO58" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AP58" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AQ58" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -6275,131 +6411,134 @@
       <c r="P59" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="Q59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R59" s="3">
         <v>81476000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>77358000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>81237000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>94232000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>101616000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>97995000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>98102000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>93872000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>90905000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>83454000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>80129000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>71002000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>83043000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>82049000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>81887000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>79627000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>71297000</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>83034000</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>80599000</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>79668000</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>79471000</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>111603200</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>105725300</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>103261300</v>
       </c>
-      <c r="AO59" s="3">
+      <c r="AP59" s="3">
         <v>67883100</v>
       </c>
-      <c r="AP59" s="3">
+      <c r="AQ59" s="3">
         <v>101627000</v>
       </c>
     </row>
-    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>2400000</v>
+      </c>
+      <c r="E60" s="3">
         <v>2768000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>2923000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>2979000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>2908000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>2551000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>2861000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1765000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1610000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>1613000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>1122000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>1192000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>1444000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>1471000</v>
       </c>
-      <c r="Q60" s="3">
-        <v>0</v>
-      </c>
       <c r="R60" s="3">
         <v>0</v>
       </c>
@@ -6475,252 +6614,261 @@
       <c r="AP60" s="3">
         <v>0</v>
       </c>
+      <c r="AQ60" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>2177000</v>
+      </c>
+      <c r="E61" s="3">
         <v>2157000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>1927000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>1783000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>1928000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>2374000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>2416000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>2441000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>2015000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>2025000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>2451000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>2448000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>2485000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>2461000</v>
-      </c>
-      <c r="Q61" s="3">
-        <v>2094000</v>
       </c>
       <c r="R61" s="3">
         <v>2094000</v>
       </c>
       <c r="S61" s="3">
+        <v>2094000</v>
+      </c>
+      <c r="T61" s="3">
         <v>2385000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>2406000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>2595000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>2970000</v>
-      </c>
-      <c r="W61" s="3">
-        <v>2969000</v>
       </c>
       <c r="X61" s="3">
         <v>2969000</v>
       </c>
       <c r="Y61" s="3">
+        <v>2969000</v>
+      </c>
+      <c r="Z61" s="3">
         <v>3044000</v>
-      </c>
-      <c r="Z61" s="3">
-        <v>3043000</v>
       </c>
       <c r="AA61" s="3">
         <v>3043000</v>
       </c>
       <c r="AB61" s="3">
-        <v>3042000</v>
+        <v>3043000</v>
       </c>
       <c r="AC61" s="3">
         <v>3042000</v>
       </c>
       <c r="AD61" s="3">
-        <v>3041000</v>
+        <v>3042000</v>
       </c>
       <c r="AE61" s="3">
         <v>3041000</v>
       </c>
       <c r="AF61" s="3">
-        <v>3136000</v>
+        <v>3041000</v>
       </c>
       <c r="AG61" s="3">
         <v>3136000</v>
       </c>
       <c r="AH61" s="3">
+        <v>3136000</v>
+      </c>
+      <c r="AI61" s="3">
         <v>3459000</v>
-      </c>
-      <c r="AI61" s="3">
-        <v>3458000</v>
       </c>
       <c r="AJ61" s="3">
         <v>3458000</v>
       </c>
       <c r="AK61" s="3">
+        <v>3458000</v>
+      </c>
+      <c r="AL61" s="3">
         <v>3123000</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>3122200</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>2726200</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>2725700</v>
       </c>
-      <c r="AO61" s="3">
+      <c r="AP61" s="3">
         <v>3550000</v>
       </c>
-      <c r="AP61" s="3">
+      <c r="AQ61" s="3">
         <v>3548500</v>
       </c>
     </row>
-    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>171727000</v>
+      </c>
+      <c r="E62" s="3">
         <v>161802000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>166636000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>165603000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>161047000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>152664000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>152274000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>156145000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>151786000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>152122000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>147109000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>140666000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>145159000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>141589000</v>
       </c>
-      <c r="Q62" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="R62" s="3">
+      <c r="R62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S62" s="3">
         <v>196000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>205000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>213000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>226000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>274000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>304000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>333000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>18976000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>18607000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>18465000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>18414000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>18966000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>409000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>445000</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>465000</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>18454000</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>516000</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>527000</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>56998000</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>58827000</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>542200</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AN62" s="3">
         <v>636800</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AO62" s="3">
         <v>656000</v>
       </c>
-      <c r="AO62" s="3">
+      <c r="AP62" s="3">
         <v>60250000</v>
       </c>
-      <c r="AP62" s="3">
+      <c r="AQ62" s="3">
         <v>631400</v>
       </c>
     </row>
-    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6841,8 +6989,11 @@
       <c r="AP63" s="3">
         <v>0</v>
       </c>
+      <c r="AQ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6963,8 +7114,11 @@
       <c r="AP64" s="3">
         <v>0</v>
       </c>
+      <c r="AQ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -7085,130 +7239,136 @@
       <c r="AP65" s="3">
         <v>0</v>
       </c>
+      <c r="AQ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>176304000</v>
+      </c>
+      <c r="E66" s="3">
         <v>166727000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>171820000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>170365000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>165883000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>157589000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>157882000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>160351000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>155411000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>155760000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>151032000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>144306000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>149088000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>145521000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>143257000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>139955000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>143004000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>155608000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>163009000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>160028000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>159832000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>154930000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>170408000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>161809000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>157386000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>148305000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>159651000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>156299000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>155098000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>152920000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>147217000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>156513000</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>154280000</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>210446000</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>212523000</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>212990900</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>206486600</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>204135100</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AP66" s="3">
         <v>201590000</v>
       </c>
-      <c r="AP66" s="3">
+      <c r="AQ66" s="3">
         <v>203416200</v>
       </c>
     </row>
-    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -7251,8 +7411,9 @@
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
       <c r="AP67" s="3"/>
+      <c r="AQ67" s="3"/>
     </row>
-    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7373,8 +7534,11 @@
       <c r="AP68" s="3">
         <v>0</v>
       </c>
+      <c r="AQ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7495,8 +7659,11 @@
       <c r="AP69" s="3">
         <v>0</v>
       </c>
+      <c r="AQ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7617,8 +7784,11 @@
       <c r="AP70" s="3">
         <v>0</v>
       </c>
+      <c r="AQ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7739,130 +7909,136 @@
       <c r="AP71" s="3">
         <v>0</v>
       </c>
+      <c r="AQ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>1562000</v>
+      </c>
+      <c r="E72" s="3">
         <v>1511000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>1392000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>1301000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>1170000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>1052000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>954000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>907000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>855000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>697000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>505000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>302000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>40000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-118000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-201000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-994000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-1201000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-1269000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-1310000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-3238000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-3394000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-3857000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-4957000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-5152000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-4833000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-4766000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-4718000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-11665000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-11785000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>-12011000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>-11732000</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>-11853000</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>-11995000</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>-12161000</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>-12719000</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>-9655600</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>-9804200</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>-9971400</v>
       </c>
-      <c r="AO72" s="3">
+      <c r="AP72" s="3">
         <v>-9742000</v>
       </c>
-      <c r="AP72" s="3">
+      <c r="AQ72" s="3">
         <v>-9310300</v>
       </c>
     </row>
-    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7983,8 +8159,11 @@
       <c r="AP73" s="3">
         <v>0</v>
       </c>
+      <c r="AQ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -8105,8 +8284,11 @@
       <c r="AP74" s="3">
         <v>0</v>
       </c>
+      <c r="AQ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -8227,130 +8409,136 @@
       <c r="AP75" s="3">
         <v>0</v>
       </c>
+      <c r="AQ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>4685000</v>
+      </c>
+      <c r="E76" s="3">
         <v>4658000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>4953000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>4957000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>4629000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>4383000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>4005000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>4719000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>4043000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>4153000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>4193000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>3127000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>3697000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>3954000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>3349000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>4093000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>4516000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>6198000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>8253000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>8389000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>8362000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>7931000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>10110000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>9657000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>9548000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>7427000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>9339000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>10551000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>10064000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>9065000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>8213000</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>8523000</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>8460000</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>9378000</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>10009000</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>13653000</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>13352200</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>12890400</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AP76" s="3">
         <v>12995000</v>
       </c>
-      <c r="AP76" s="3">
+      <c r="AQ76" s="3">
         <v>15206000</v>
       </c>
     </row>
-    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8471,257 +8659,266 @@
       <c r="AP77" s="3">
         <v>0</v>
       </c>
+      <c r="AQ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44742</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44651</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44561</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44469</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44377</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44286</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44196</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44104</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>44012</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43921</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43830</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43738</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43646</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43555</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43465</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43373</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43190</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43100</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>43008</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42916</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42825</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AP80" s="2">
         <v>42735</v>
       </c>
-      <c r="AP80" s="2">
+      <c r="AQ80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>94000</v>
+      </c>
+      <c r="E81" s="3">
         <v>182000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>140000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>192000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>166000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>156000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>97000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>114000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>205000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>251000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>122000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>262000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>158000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>83000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>190000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>166000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>64000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>54000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>403000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>142000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>459000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>1086000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>260000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-499000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-66000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-98000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-785000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>107000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>226000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>64000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>121000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>142000</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>166000</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>446000</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>-3164300</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>149000</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>167000</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>-143000</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AP81" s="3">
         <v>-327000</v>
       </c>
-      <c r="AP81" s="3">
+      <c r="AQ81" s="3">
         <v>-248100</v>
       </c>
     </row>
-    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8764,8 +8961,9 @@
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
       <c r="AP82" s="3"/>
+      <c r="AQ82" s="3"/>
     </row>
-    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -8799,17 +8997,17 @@
       <c r="M83" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N83" s="3">
+      <c r="N83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O83" s="3">
         <v>-22000</v>
       </c>
-      <c r="O83" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="P83" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q83" s="3">
-        <v>0</v>
+      <c r="Q83" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R83" s="3">
         <v>0</v>
@@ -8886,8 +9084,11 @@
       <c r="AP83" s="3">
         <v>0</v>
       </c>
+      <c r="AQ83" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -9008,8 +9209,11 @@
       <c r="AP84" s="3">
         <v>0</v>
       </c>
+      <c r="AQ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -9130,8 +9334,11 @@
       <c r="AP85" s="3">
         <v>0</v>
       </c>
+      <c r="AQ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -9252,8 +9459,11 @@
       <c r="AP86" s="3">
         <v>0</v>
       </c>
+      <c r="AQ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -9374,8 +9584,11 @@
       <c r="AP87" s="3">
         <v>0</v>
       </c>
+      <c r="AQ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9496,130 +9709,136 @@
       <c r="AP88" s="3">
         <v>0</v>
       </c>
+      <c r="AQ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>503000</v>
+      </c>
+      <c r="E89" s="3">
         <v>-36000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>557000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>168000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>742000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-179000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>79000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>719000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>316000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>231000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>364000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>403000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>715000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>156000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>219000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>418000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>296000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>419000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>140000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>121000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>747000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-936000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>421000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>788000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>508000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-76000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>459000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>302000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>418000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>131000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>234000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>580000</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>653000</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>401000</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>456000</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>570000</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>605800</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>-49800</v>
       </c>
-      <c r="AO89" s="3">
+      <c r="AP89" s="3">
         <v>3591000</v>
       </c>
-      <c r="AP89" s="3">
+      <c r="AQ89" s="3">
         <v>819700</v>
       </c>
     </row>
-    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9662,8 +9881,9 @@
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
       <c r="AP90" s="3"/>
+      <c r="AQ90" s="3"/>
     </row>
-    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -9706,8 +9926,8 @@
       <c r="P91" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q91" s="3">
-        <v>0</v>
+      <c r="Q91" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R91" s="3">
         <v>0</v>
@@ -9766,26 +9986,29 @@
       <c r="AJ91" s="3">
         <v>0</v>
       </c>
-      <c r="AK91" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AL91" s="3">
+      <c r="AK91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AM91" s="3">
         <v>-9700</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-15700</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>-10400</v>
       </c>
-      <c r="AO91" s="3">
+      <c r="AP91" s="3">
         <v>-66700</v>
       </c>
-      <c r="AP91" s="3">
+      <c r="AQ91" s="3">
         <v>-25800</v>
       </c>
     </row>
-    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9906,8 +10129,11 @@
       <c r="AP92" s="3">
         <v>0</v>
       </c>
+      <c r="AQ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -10028,130 +10254,136 @@
       <c r="AP93" s="3">
         <v>0</v>
       </c>
+      <c r="AQ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>724000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-352000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-372000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-718000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-524000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>245000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-23000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-486000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-92000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>1082000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>833000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>430000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>797000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>472000</v>
       </c>
-      <c r="Q94" s="3">
-        <v>0</v>
-      </c>
       <c r="R94" s="3">
+        <v>0</v>
+      </c>
+      <c r="S94" s="3">
         <v>-372000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-1171000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-403000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-578000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-600000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>181000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>670000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-636000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-1825000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-139000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-811000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-374000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-954000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>117000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-44000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-333000</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-36000</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-149000</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>236000</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-145000</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-1581300</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>-892500</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>190800</v>
       </c>
-      <c r="AO94" s="3">
+      <c r="AP94" s="3">
         <v>-3683000</v>
       </c>
-      <c r="AP94" s="3">
+      <c r="AQ94" s="3">
         <v>-1924000</v>
       </c>
     </row>
-    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -10194,130 +10426,134 @@
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
       <c r="AP95" s="3"/>
+      <c r="AQ95" s="3"/>
     </row>
-    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>46000</v>
+      </c>
+      <c r="E96" s="3">
         <v>44000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>45000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>43000</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>47000</v>
-      </c>
-      <c r="H96" s="3">
-        <v>43000</v>
       </c>
       <c r="I96" s="3">
         <v>43000</v>
       </c>
       <c r="J96" s="3">
+        <v>43000</v>
+      </c>
+      <c r="K96" s="3">
         <v>44000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>43000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>41000</v>
-      </c>
-      <c r="M96" s="3">
-        <v>42000</v>
       </c>
       <c r="N96" s="3">
         <v>42000</v>
       </c>
       <c r="O96" s="3">
+        <v>42000</v>
+      </c>
+      <c r="P96" s="3">
         <v>23000</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>20000</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-20000</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-22000</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-20000</v>
-      </c>
-      <c r="T96" s="3">
-        <v>-21000</v>
       </c>
       <c r="U96" s="3">
         <v>-21000</v>
       </c>
       <c r="V96" s="3">
+        <v>-21000</v>
+      </c>
+      <c r="W96" s="3">
         <v>-19000</v>
-      </c>
-      <c r="W96" s="3">
-        <v>-20000</v>
       </c>
       <c r="X96" s="3">
         <v>-20000</v>
       </c>
       <c r="Y96" s="3">
+        <v>-20000</v>
+      </c>
+      <c r="Z96" s="3">
         <v>-18000</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-58000</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-19000</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-20000</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-21000</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-20000</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-2000</v>
-      </c>
-      <c r="AF96" s="3">
-        <v>-1000</v>
       </c>
       <c r="AG96" s="3">
         <v>-1000</v>
       </c>
       <c r="AH96" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="AI96" s="3">
         <v>-2000</v>
       </c>
-      <c r="AI96" s="3">
+      <c r="AJ96" s="3">
         <v>-1000</v>
       </c>
-      <c r="AJ96" s="3">
+      <c r="AK96" s="3">
         <v>-2000</v>
       </c>
-      <c r="AK96" s="3">
+      <c r="AL96" s="3">
         <v>-2500</v>
       </c>
-      <c r="AL96" s="3">
+      <c r="AM96" s="3">
         <v>-1700</v>
-      </c>
-      <c r="AM96" s="3">
-        <v>-1900</v>
       </c>
       <c r="AN96" s="3">
         <v>-1900</v>
       </c>
       <c r="AO96" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="AP96" s="3">
         <v>-8000</v>
       </c>
-      <c r="AP96" s="3">
+      <c r="AQ96" s="3">
         <v>-2000</v>
       </c>
     </row>
-    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -10438,8 +10674,11 @@
       <c r="AP97" s="3">
         <v>0</v>
       </c>
+      <c r="AQ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10560,8 +10799,11 @@
       <c r="AP98" s="3">
         <v>0</v>
       </c>
+      <c r="AQ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10682,130 +10924,136 @@
       <c r="AP99" s="3">
         <v>0</v>
       </c>
+      <c r="AQ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-1232000</v>
+      </c>
+      <c r="E100" s="3">
         <v>130000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-113000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>505000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>93000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-570000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-87000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>132000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-220000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-1255000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-996000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-1265000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-987000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-811000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-147000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-150000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>732000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-407000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-55000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>391000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-333000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-268000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>588000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>1114000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-158000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>727000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>11000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>546000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-86000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-592000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-152000</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-289000</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-926000</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-397000</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-562400</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>414200</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>556600</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>-753400</v>
       </c>
-      <c r="AO100" s="3">
+      <c r="AP100" s="3">
         <v>495400</v>
       </c>
-      <c r="AP100" s="3">
+      <c r="AQ100" s="3">
         <v>71300</v>
       </c>
     </row>
-    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -10848,8 +11096,8 @@
       <c r="P101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q101" s="3">
-        <v>0</v>
+      <c r="Q101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R101" s="3">
         <v>0</v>
@@ -10926,126 +11174,132 @@
       <c r="AP101" s="3">
         <v>0</v>
       </c>
+      <c r="AQ101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-5000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-258000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>72000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-45000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>311000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-504000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-31000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>365000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>4000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>58000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>201000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-432000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>525000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-183000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>72000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-104000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-143000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-391000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-493000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-88000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>595000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-534000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>373000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>77000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>211000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-160000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>96000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-106000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>449000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-505000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-251000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>255000</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-422000</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>240000</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>-251200</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>-600500</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>269100</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>-612400</v>
       </c>
-      <c r="AO102" s="3">
+      <c r="AP102" s="3">
         <v>398000</v>
       </c>
-      <c r="AP102" s="3">
+      <c r="AQ102" s="3">
         <v>-1033000</v>
       </c>
     </row>
